--- a/Result/profitability/6855.xlsx
+++ b/Result/profitability/6855.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM25"/>
+  <dimension ref="A1:AM26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3605,6 +3605,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6855</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>178</v>
+      </c>
+      <c r="D26" t="n">
+        <v>91</v>
+      </c>
+      <c r="E26" t="n">
+        <v>87</v>
+      </c>
+      <c r="F26" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="G26" t="n">
+        <v>63</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>35.29%</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>62</v>
+      </c>
+      <c r="K26" t="n">
+        <v>49</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.035</v>
+      </c>
+      <c r="N26" t="n">
+        <v>49.4925</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.0900000000000003</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.04433497536945818</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.06000000000000227</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.001230769230769369</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-3.55421686746988</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-1.349999999999994</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-0.026913875598086</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK26" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
